--- a/Dataset/Lexical-words-Dataset/Bwords-dataset(draft).xlsx
+++ b/Dataset/Lexical-words-Dataset/Bwords-dataset(draft).xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="180">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="207">
   <si>
     <t>IPA</t>
   </si>
@@ -212,18 +212,12 @@
     <t>غئیِنٚ</t>
   </si>
   <si>
-    <t>ghayeiń</t>
-  </si>
-  <si>
     <t>graps</t>
   </si>
   <si>
     <t>قرقَمُش</t>
   </si>
   <si>
-    <t>qarqamosh</t>
-  </si>
-  <si>
     <t>hen</t>
   </si>
   <si>
@@ -296,9 +290,6 @@
     <t>ہغوࣷر</t>
   </si>
   <si>
-    <t>haghor</t>
-  </si>
-  <si>
     <t>horse</t>
   </si>
   <si>
@@ -564,6 +555,96 @@
   </si>
   <si>
     <t>Some days before</t>
+  </si>
+  <si>
+    <t>sãnsān Ḍim iṣqam ayaś yaare han najai emet'n ole guyechamam</t>
+  </si>
+  <si>
+    <t>سآن ساࣷن ڈیم اِݜقم ایَش یارے ہن نجائی ایࣷمیࣷتن اُڵےࣷ گوے ڎَ مم</t>
+  </si>
+  <si>
+    <t>Some days before, I saw you under the blue sky in an unfamiliar place.</t>
+  </si>
+  <si>
+    <t>کچھ دن پہلے نیلے آسمان کے نیچے ایک انجان جگہ پر آپ کو دیکھا تھا۔</t>
+  </si>
+  <si>
+    <t>(N/A – fixed phrase, not normally inflected)</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Time &amp; Temporal Expressions → Past Reference</t>
+  </si>
+  <si>
+    <t xml:space="preserve">بُش میاو میاو نِت شولتا گلی </t>
+  </si>
+  <si>
+    <t>ġayeiń</t>
+  </si>
+  <si>
+    <t>haġor</t>
+  </si>
+  <si>
+    <t>buśha meao meao net śholta gali</t>
+  </si>
+  <si>
+    <t>The cat meowed and went onto the roof</t>
+  </si>
+  <si>
+    <t>بلی میاو میاو کرکے چھت پر گئی</t>
+  </si>
+  <si>
+    <t>/buʃ/</t>
+  </si>
+  <si>
+    <t>cat: animal</t>
+  </si>
+  <si>
+    <t>بلی:جانور</t>
+  </si>
+  <si>
+    <t>buśhanz (plural: cats)</t>
+  </si>
+  <si>
+    <t>/buʃanz/</t>
+  </si>
+  <si>
+    <t>Animals → Domestic Animals → Cat</t>
+  </si>
+  <si>
+    <t>/pʰopos/</t>
+  </si>
+  <si>
+    <t>A broomstick, a cleaning tool made of bundled sticks used for sweeping floors and courtyards.</t>
+  </si>
+  <si>
+    <t>qarqamośh</t>
+  </si>
+  <si>
+    <t>گھریلو صفائی کے لیے استعمال ہونے والا ایک آلہ جو لکڑی یا تنکوں کے گچھے کو مضبوطی سے باندھ کر بنایا جاتا ہے۔ اسے فرش، آنگن یا صحن وغیرہ صاف کرنے کے لیے استعمال کیا جاتا ہے۔</t>
+  </si>
+  <si>
+    <t>ہِن ہیࣷڵیࣷسے نے پھوࣷپوࣷس نِیا  پھُو ہِلِنٚکِݜ یکڵاࣷ تم بئی</t>
+  </si>
+  <si>
+    <t>hen hellesene pʰopos neya phu  hilingkiṣ yakalla tambai</t>
+  </si>
+  <si>
+    <t>A boy is going towards the fire with a broomstick</t>
+  </si>
+  <si>
+    <t>ایک لڑکا جاڑو لے کر آگ کی طرف جا رہا ہے</t>
+  </si>
+  <si>
+    <t>Phopośhiń (plural: broomsticks)</t>
+  </si>
+  <si>
+    <t>/pʰopoʃiŋ/</t>
+  </si>
+  <si>
+    <t>Household / Tools / Cleaning</t>
   </si>
 </sst>
 </file>
@@ -1009,15 +1090,15 @@
     <col min="5" max="5" width="31.77734375" style="10" customWidth="1"/>
     <col min="6" max="6" width="20.109375" style="10" customWidth="1"/>
     <col min="7" max="7" width="24.77734375" style="10" customWidth="1"/>
-    <col min="8" max="8" width="39.88671875" style="10" customWidth="1"/>
-    <col min="9" max="9" width="37.88671875" style="10" customWidth="1"/>
-    <col min="10" max="10" width="28.109375" style="10" customWidth="1"/>
-    <col min="11" max="11" width="30.6640625" style="10" customWidth="1"/>
-    <col min="12" max="12" width="33.109375" style="10" customWidth="1"/>
-    <col min="13" max="13" width="25" style="10" customWidth="1"/>
-    <col min="14" max="14" width="27.88671875" style="10" customWidth="1"/>
+    <col min="8" max="8" width="74.88671875" style="10" customWidth="1"/>
+    <col min="9" max="9" width="56.33203125" style="10" customWidth="1"/>
+    <col min="10" max="10" width="51.5546875" style="10" customWidth="1"/>
+    <col min="11" max="11" width="53.6640625" style="10" customWidth="1"/>
+    <col min="12" max="12" width="58.21875" style="10" customWidth="1"/>
+    <col min="13" max="13" width="46.5546875" style="10" customWidth="1"/>
+    <col min="14" max="14" width="36.44140625" style="10" customWidth="1"/>
     <col min="15" max="15" width="18.33203125" style="10" customWidth="1"/>
-    <col min="16" max="16" width="31.33203125" style="10" customWidth="1"/>
+    <col min="16" max="16" width="39.77734375" style="10" customWidth="1"/>
     <col min="17" max="17" width="17.6640625" style="10" customWidth="1"/>
     <col min="18" max="18" width="12.88671875" style="10" customWidth="1"/>
     <col min="19" max="19" width="18.5546875" style="10" customWidth="1"/>
@@ -1026,61 +1107,61 @@
   <sheetData>
     <row r="1" spans="1:19" s="6" customFormat="1" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F1" s="7" t="s">
         <v>0</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="L1" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="M1" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="N1" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="O1" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="P1" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="Q1" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="O1" s="6" t="s">
+      <c r="R1" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="P1" s="6" t="s">
+      <c r="S1" s="6" t="s">
         <v>110</v>
-      </c>
-      <c r="Q1" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="R1" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="S1" s="6" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
@@ -1097,40 +1178,40 @@
         <v>3</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="K2" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="L2" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="M2" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>151</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="K2" s="10" t="s">
+      <c r="N2" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="L2" s="10" t="s">
+      <c r="O2" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="P2" s="10" t="s">
         <v>160</v>
-      </c>
-      <c r="M2" s="10" t="s">
-        <v>159</v>
-      </c>
-      <c r="N2" s="10" t="s">
-        <v>161</v>
-      </c>
-      <c r="O2" s="10" t="s">
-        <v>162</v>
-      </c>
-      <c r="P2" s="10" t="s">
-        <v>163</v>
       </c>
       <c r="Q2" s="12">
         <v>45912</v>
@@ -1139,7 +1220,7 @@
         <v>45912</v>
       </c>
       <c r="S2" s="10" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
@@ -1156,40 +1237,40 @@
         <v>6</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="G3" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="H3" s="2" t="s">
+      <c r="K3" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="L3" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="M3" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="N3" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="O3" s="10" t="s">
         <v>170</v>
       </c>
-      <c r="K3" s="10" t="s">
-        <v>165</v>
-      </c>
-      <c r="L3" s="10" t="s">
-        <v>166</v>
-      </c>
-      <c r="M3" s="10" t="s">
+      <c r="P3" s="10" t="s">
         <v>171</v>
-      </c>
-      <c r="N3" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="O3" s="10" t="s">
-        <v>173</v>
-      </c>
-      <c r="P3" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="Q3" s="12">
         <v>45912</v>
@@ -1198,7 +1279,7 @@
         <v>45912</v>
       </c>
       <c r="S3" s="10" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
@@ -1215,21 +1296,50 @@
         <v>9</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="F4" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="G4" s="11" t="s">
+        <v>175</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="I4" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="K4" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="G4" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="H4" s="3" t="s">
+      <c r="L4" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="I4" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="J4" s="1"/>
+      <c r="M4" s="10" t="s">
+        <v>180</v>
+      </c>
+      <c r="N4" s="10" t="s">
+        <v>181</v>
+      </c>
+      <c r="O4" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="P4" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q4" s="12">
+        <v>45912</v>
+      </c>
+      <c r="R4" s="12">
+        <v>45912</v>
+      </c>
+      <c r="S4" s="10" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="5" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A5" s="8">
@@ -1239,19 +1349,56 @@
         <v>10</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>11</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
+        <v>114</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="K5" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="L5" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="M5" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="N5" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="O5" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="P5" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="Q5" s="12">
+        <v>45912</v>
+      </c>
+      <c r="R5" s="12">
+        <v>45912</v>
+      </c>
+      <c r="S5" s="10" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="6" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6" s="8">
@@ -1267,13 +1414,50 @@
         <v>14</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
+        <v>115</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="K6" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="L6" s="10" t="s">
+        <v>202</v>
+      </c>
+      <c r="M6" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="N6" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="O6" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="P6" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="Q6" s="12">
+        <v>45912</v>
+      </c>
+      <c r="R6" s="12">
+        <v>45912</v>
+      </c>
+      <c r="S6" s="10" t="s">
+        <v>161</v>
+      </c>
     </row>
     <row r="7" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A7" s="8">
@@ -1289,7 +1473,7 @@
         <v>17</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
@@ -1311,7 +1495,7 @@
         <v>20</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
@@ -1333,7 +1517,7 @@
         <v>23</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="F9" s="1"/>
       <c r="G9" s="1"/>
@@ -1355,7 +1539,7 @@
         <v>26</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
@@ -1377,7 +1561,7 @@
         <v>29</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
@@ -1399,7 +1583,7 @@
         <v>32</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
@@ -1421,7 +1605,7 @@
         <v>35</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
@@ -1440,10 +1624,10 @@
         <v>37</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
@@ -1465,7 +1649,7 @@
         <v>40</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="F15" s="4"/>
       <c r="G15" s="4"/>
@@ -1487,7 +1671,7 @@
         <v>43</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="F16" s="4"/>
       <c r="G16" s="4"/>
@@ -1509,7 +1693,7 @@
         <v>46</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
@@ -1531,7 +1715,7 @@
         <v>49</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
@@ -1553,7 +1737,7 @@
         <v>52</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
@@ -1575,7 +1759,7 @@
         <v>55</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
@@ -1591,13 +1775,13 @@
         <v>56</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>57</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
@@ -1619,7 +1803,7 @@
         <v>60</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
@@ -1635,13 +1819,13 @@
         <v>61</v>
       </c>
       <c r="C23" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="D23" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="D23" s="1" t="s">
-        <v>63</v>
-      </c>
       <c r="E23" s="1" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="F23" s="4"/>
       <c r="G23" s="4"/>
@@ -1654,16 +1838,16 @@
         <v>45</v>
       </c>
       <c r="B24" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="D24" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="C24" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="E24" s="1" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
@@ -1676,16 +1860,16 @@
         <v>46</v>
       </c>
       <c r="B25" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="D25" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="C25" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>69</v>
-      </c>
       <c r="E25" s="1" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
@@ -1698,16 +1882,16 @@
         <v>47</v>
       </c>
       <c r="B26" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D26" s="1" t="s">
         <v>70</v>
       </c>
-      <c r="C26" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="E26" s="1" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F26" s="4"/>
       <c r="G26" s="4"/>
@@ -1720,16 +1904,16 @@
         <v>48</v>
       </c>
       <c r="B27" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D27" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C27" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>75</v>
-      </c>
       <c r="E27" s="1" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="F27" s="4"/>
       <c r="G27" s="4"/>
@@ -1742,16 +1926,16 @@
         <v>49</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F28" s="4"/>
       <c r="G28" s="4"/>
@@ -1764,16 +1948,16 @@
         <v>51</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>80</v>
-      </c>
       <c r="E29" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="F29" s="1"/>
       <c r="G29" s="1"/>
@@ -1786,16 +1970,16 @@
         <v>52</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="F30" s="4"/>
       <c r="G30" s="4"/>
@@ -1809,16 +1993,16 @@
         <v>53</v>
       </c>
       <c r="B31" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D31" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="C31" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>85</v>
-      </c>
       <c r="E31" s="4" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="F31" s="4"/>
       <c r="G31" s="4"/>
@@ -1832,16 +2016,16 @@
         <v>54</v>
       </c>
       <c r="B32" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D32" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C32" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>88</v>
-      </c>
       <c r="E32" s="1" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="F32" s="4"/>
       <c r="G32" s="4"/>
@@ -1855,16 +2039,16 @@
         <v>57</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>90</v>
+        <v>186</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="F33" s="2"/>
       <c r="G33" s="2"/>
@@ -1878,16 +2062,16 @@
         <v>58</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="F34" s="2"/>
       <c r="G34" s="2"/>
@@ -1901,16 +2085,16 @@
         <v>59</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F35" s="2"/>
       <c r="G35" s="2"/>

--- a/Dataset/Lexical-words-Dataset/Bwords-dataset(draft).xlsx
+++ b/Dataset/Lexical-words-Dataset/Bwords-dataset(draft).xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="209">
   <si>
     <t>IPA</t>
   </si>
@@ -645,6 +645,12 @@
   </si>
   <si>
     <t>Household / Tools / Cleaning</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> تلٚ آصفؔ اےࣷ ہِݩتاڵ دُوَّڵ دُوَّڵ بِم</t>
+  </si>
+  <si>
+    <t>tall asifa he</t>
   </si>
 </sst>
 </file>
@@ -1479,7 +1485,12 @@
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
+      <c r="J7" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="8" spans="1:19" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A8" s="8">
